--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>4,4 + 5,2 + 3,9 = 13,4</t>
+          <t>4,5 + 5,3 + 4,2 = 13,9</t>
         </is>
       </c>
       <c r="F5" s="34" t="inlineStr">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>224.7</v>
+        <v>268.1</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>273.9</v>
+        <v>325.5</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 250,7 + котлованы 23,2 = 273,9</t>
+          <t>траншеи 301,3 + котлованы 24,2 = 325,5</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>18.6</v>
+        <v>21.7</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>99.40000000000001</v>
+        <v>296.9</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" s="36" t="inlineStr">
         <is>
-          <t>К1-б3, К2-ЛК, В1-н, Др-К</t>
+          <t>К1-б3, К2-ЛК, В1-н, Др-1/2, Др-2/3, Др-4/3, Др-К</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>56.5</v>
+        <v>70.2</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 48</t>
+          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 52</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="13" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
           <t>8</t>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>Устройство щебёночной призмы вокруг дренажа в обёртке из геотекстиля</t>
+          <t>Засыпка траншей и пазух колодцев в зоне заезда песком на всю глубину слоями с уплотнением, Купл ≥ 0,95</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -1168,12 +1168,12 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>33</v>
+        <v>85.2</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 49</t>
+          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 52</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
-          <t>5 6 8 11</t>
+          <t>2 3 8 11</t>
         </is>
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>геотекстиль — поз. 50</t>
+          <t>полоса 3,2 м вдоль западного и восточного заборов, площадка у гаража</t>
         </is>
       </c>
     </row>
@@ -1200,21 +1200,21 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Укладка геотекстиля с нахлёстом 0,3 м</t>
+          <t>Устройство щебёночной призмы вокруг дренажа в обёртке из геотекстиля</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м³</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>360</v>
+        <v>33</v>
       </c>
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 50</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 53</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1224,164 +1224,164 @@
       </c>
       <c r="H14" s="30" t="inlineStr">
         <is>
+          <t>5 6 8 11</t>
+        </is>
+      </c>
+      <c r="I14" s="36" t="inlineStr">
+        <is>
+          <t>геотекстиль — поз. 54</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" thickBot="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Укладка геотекстиля с нахлёстом 0,3 м</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>360</v>
+      </c>
+      <c r="E15" s="33" t="n"/>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 54</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H15" s="30" t="inlineStr">
+        <is>
           <t>8 11</t>
         </is>
       </c>
-      <c r="I14" s="36" t="n"/>
-    </row>
-    <row r="15" ht="45" customHeight="1" thickBot="1">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="I15" s="36" t="n"/>
+    </row>
+    <row r="16" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Обратная засыпка траншей и пазух местным грунтом без камней слоями 0,2–0,3 м с уплотнением</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>м³</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n">
-        <v>197</v>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>287,2 − 90,3 = 197,0</t>
-        </is>
-      </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="D16" s="32" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>339,4 − 180,8 = 158,6</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-НВК, см. листы 2, 8</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>2 8</t>
         </is>
       </c>
-      <c r="I15" s="36" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>под проездами — песком на всю глубину, Купл ≥ 0,95</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
+    <row r="17" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Погрузка и вывоз лишнего грунта (объём песка, щебня, труб и колодцев)</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>м³</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="34" t="inlineStr"/>
-      <c r="G16" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="inlineStr"/>
-      <c r="I16" s="36" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="D17" s="32" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="34" t="inlineStr"/>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="inlineStr"/>
+      <c r="I17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Водопровод В1 (ввод) и подводка полива</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="29" t="n"/>
-    </row>
-    <row r="18" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="29" t="n"/>
+    </row>
+    <row r="19" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>Прокладка трубопровода ПЭ 100 SDR11 32×3,0 на глубине не менее 1,6 м с соединением электросварными муфтами и отводами</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D19" s="32" t="n">
         <v>17</v>
-      </c>
-      <c r="E18" s="33" t="n"/>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 7, 8; И05.09.26-НВК.СО, поз. 1, 3, 4</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="inlineStr">
-        <is>
-          <t>3 7 8 9</t>
-        </is>
-      </c>
-      <c r="I18" s="36" t="inlineStr">
-        <is>
-          <t>повороты 45° — изгибом трубы</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка подводки полива ПЭ 100 SDR11 25×2,3 с компрессионными фитингами</t>
-        </is>
-      </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>3</v>
       </c>
       <c r="E19" s="33" t="n"/>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 2, 10</t>
+          <t>И05.09.26-НВК, см. листы 3, 7, 8; И05.09.26-НВК.СО, поз. 1, 3, 4</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1391,16 +1391,16 @@
       </c>
       <c r="H19" s="30" t="inlineStr">
         <is>
-          <t>3 7 9</t>
+          <t>3 7 8 9</t>
         </is>
       </c>
       <c r="I19" s="36" t="inlineStr">
         <is>
-          <t>уклон 0,01 к КП-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customFormat="1" customHeight="1" s="4">
+          <t>повороты 45° — изгибом трубы</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customFormat="1" customHeight="1" s="4">
       <c r="A20" s="30" t="inlineStr">
         <is>
           <t>14</t>
@@ -1408,21 +1408,21 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>Установка крана шарового подземного с телескопическим штоком и ковером на бетонной подушке</t>
+          <t>Прокладка сезонных линий полива ПЭ 100 SDR11 25×2,3 с компрессионными фитингами: КХ-8н до КП-1, В1-Бс от КП-1 к беседке</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E20" s="33" t="n"/>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 5, 6</t>
+          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 2, 10, 11</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1435,7 +1435,11 @@
           <t>3 7 9</t>
         </is>
       </c>
-      <c r="I20" s="36" t="n"/>
+      <c r="I20" s="36" t="inlineStr">
+        <is>
+          <t>уклон к КП-1: 0,01 и 0,003; глубина В1-Бс 0,7–0,8 м</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A21" s="30" t="inlineStr">
@@ -1445,21 +1449,21 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Протаскивание трубы В1 в футляре ПНД Ø110 под крыльцом 1.6</t>
+          <t>Протаскивание линии В1-Бс в футляре ПНД Ø63 в зоне заезда</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E21" s="33" t="n"/>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 7; И05.09.26-НВК.СО, поз. 7</t>
+          <t>И05.09.26-НВК, см. лист 3; И05.09.26-НВК.СО, поз. 15</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1469,7 +1473,7 @@
       </c>
       <c r="H21" s="30" t="inlineStr">
         <is>
-          <t>7 9</t>
+          <t>3 9</t>
         </is>
       </c>
       <c r="I21" s="36" t="n"/>
@@ -1482,21 +1486,21 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>Изоляция подъёма ввода скорлупой ППУ с монтажом греющего кабеля</t>
+          <t>Установка садовой колонки с краном у беседки</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" s="33" t="n"/>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 7, 8; И05.09.26-НВК.СО, поз. 8, 9</t>
+          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 14</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1506,12 +1510,12 @@
       </c>
       <c r="H22" s="30" t="inlineStr">
         <is>
-          <t>7 8 9</t>
+          <t>3 7 9</t>
         </is>
       </c>
       <c r="I22" s="36" t="inlineStr">
         <is>
-          <t>подключение кабеля — ЭОМ</t>
+          <t>сезонная, слив через КП-1</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1527,7 @@
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>Установка колодца полива КП-1 Ø400 с кранами полива и слива</t>
+          <t>Установка крана шарового подземного с телескопическим штоком и ковером на бетонной подушке</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -1537,7 +1541,7 @@
       <c r="E23" s="33" t="n"/>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7, 8; И05.09.26-НВК.СО, поз. 11, 12, 13</t>
+          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 5, 6</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1547,7 +1551,7 @@
       </c>
       <c r="H23" s="30" t="inlineStr">
         <is>
-          <t>3 7 8 9</t>
+          <t>3 7 9</t>
         </is>
       </c>
       <c r="I23" s="36" t="n"/>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>Подключение к выпуску поселкового водопровода от ВК217</t>
+          <t>Протаскивание трубы В1 в футляре ПНД Ø110 под крыльцом 1.6</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -1574,7 +1578,7 @@
       <c r="E24" s="33" t="n"/>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7</t>
+          <t>И05.09.26-НВК, см. лист 7; И05.09.26-НВК.СО, поз. 7</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -1584,53 +1588,75 @@
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
-          <t>3 7</t>
-        </is>
-      </c>
-      <c r="I24" s="36" t="inlineStr">
-        <is>
-          <t>по ТУ, с допуском ООО «Лика»</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>Канализация бытовая К1</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="n"/>
-      <c r="C25" s="28" t="n"/>
-      <c r="D25" s="28" t="n"/>
-      <c r="E25" s="28" t="n"/>
-      <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="28" t="n"/>
-      <c r="I25" s="29" t="n"/>
-    </row>
-    <row r="26" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>7 9</t>
+        </is>
+      </c>
+      <c r="I24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>Изоляция подъёма ввода скорлупой ППУ с монтажом греющего кабеля</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 7, 8; И05.09.26-НВК.СО, поз. 8, 9</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H25" s="30" t="inlineStr">
+        <is>
+          <t>7 8 9</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="inlineStr">
+        <is>
+          <t>подключение кабеля — ЭОМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (выпуски) на песчаном основании</t>
+          <t>Установка колодца полива КП-1 Ø400 с люком Т (C250) и кранами полива, ответвления к беседке и слива</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D26" s="32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="33" t="n"/>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 15, 17</t>
+          <t>И05.09.26-НВК, см. листы 3, 7, 8; И05.09.26-НВК.СО, поз. 12, 13, 16</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1640,7 +1666,7 @@
       </c>
       <c r="H26" s="30" t="inlineStr">
         <is>
-          <t>3 4 9</t>
+          <t>3 7 8 9</t>
         </is>
       </c>
       <c r="I26" s="36" t="n"/>
@@ -1648,26 +1674,26 @@
     <row r="27" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø160 (сеть бани) на песчаном основании</t>
+          <t>Подключение к выпуску поселкового водопровода от ВК217</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D27" s="32" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="E27" s="33" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 16</t>
+          <t>И05.09.26-НВК, см. листы 3, 7</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1677,53 +1703,31 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>3 4 9</t>
-        </is>
-      </c>
-      <c r="I27" s="36" t="n"/>
-    </row>
-    <row r="28" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>Установка колодцев канализационных полимерных Ø630 с лотком, шахтой и люком</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 + 1 = 3</t>
-        </is>
-      </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 18, 19, 20</t>
-        </is>
-      </c>
-      <c r="G28" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H28" s="30" t="inlineStr">
-        <is>
-          <t>3 4 8 9</t>
-        </is>
-      </c>
-      <c r="I28" s="36" t="n"/>
-    </row>
-    <row r="29" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>3 7</t>
+        </is>
+      </c>
+      <c r="I27" s="36" t="inlineStr">
+        <is>
+          <t>по ТУ, с допуском ООО «Лика»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>Канализация бытовая К1</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="29" t="n"/>
+    </row>
+    <row r="29" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>22</t>
@@ -1731,21 +1735,21 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>Врезка в существующий колодец ДК5-018: алмазное бурение отверстий в ж/б стенке, установка манжет, заделка, устройство лотков-водосливов</t>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (выпуски) на песчаном основании</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 21, 22</t>
+          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 18, 20</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1755,80 +1759,98 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
+          <t>3 4 9</t>
+        </is>
+      </c>
+      <c r="I29" s="36" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1" thickBot="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов ПП SN8 Ø160 (сеть бани) на песчаном основании</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>62</v>
+      </c>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 19</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>3 4 9</t>
+        </is>
+      </c>
+      <c r="I30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>Установка колодцев канализационных полимерных Ø630 с лотком, шахтой и люком</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 + 1 = 3</t>
+        </is>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 21, 22, 23</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H31" s="30" t="inlineStr">
+        <is>
           <t>3 4 8 10</t>
         </is>
       </c>
-      <c r="I29" s="36" t="inlineStr">
-        <is>
-          <t>узел 3 листа 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>Ливневая канализация К2. Колодец КЛ-1</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="n"/>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="29" t="n"/>
-    </row>
-    <row r="31" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит) с фасонными частями в общей траншее с дренажом</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="n">
-        <v>164</v>
-      </c>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 24, 27, 28, 29</t>
-        </is>
-      </c>
-      <c r="G31" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="inlineStr">
-        <is>
-          <t>3 5 6 8 10</t>
-        </is>
-      </c>
-      <c r="I31" s="36" t="inlineStr">
-        <is>
-          <t>выше дренажа на 0,235 м (узел 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="I31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>Подключение выпусков стояков водостоков к кольцам К2 (отводы 45°, косые тройники)</t>
+          <t>Врезка в существующий колодец ДК5-018: алмазное бурение отверстий в ж/б стенке, установка манжет, заделка, устройство лотков-водосливов</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -1837,12 +1859,12 @@
         </is>
       </c>
       <c r="D32" s="32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E32" s="33" t="n"/>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 29</t>
+          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 24, 25</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -1852,57 +1874,31 @@
       </c>
       <c r="H32" s="30" t="inlineStr">
         <is>
-          <t>5 6 8 10</t>
+          <t>3 4 8 10</t>
         </is>
       </c>
       <c r="I32" s="36" t="inlineStr">
         <is>
-          <t>ориентировочно 8 шт. — по привязке воронок</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>Установка футляров Ø160 в край плиты для выпусков водостоков</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 30</t>
-        </is>
-      </c>
-      <c r="G33" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H33" s="30" t="inlineStr">
-        <is>
-          <t>8 10</t>
-        </is>
-      </c>
-      <c r="I33" s="36" t="inlineStr">
-        <is>
-          <t>при бетонировании (КР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>узел 3 листа 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>Ливневая канализация К2. Колодец КЛ-1</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="29" t="n"/>
+    </row>
+    <row r="34" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
           <t>26</t>
@@ -1910,21 +1906,21 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>Монтаж колодца КЛ-1 из сборных ж/б элементов (днище, кольца, плита, горловина, люк, скобы)</t>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит) с фасонными частями в общей траншее с дренажом</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="E34" s="33" t="n"/>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 31, 32, 33, 34, 35, 36, 37</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 27, 30, 31, 32</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -1934,16 +1930,16 @@
       </c>
       <c r="H34" s="30" t="inlineStr">
         <is>
-          <t>3 6 8 10</t>
+          <t>3 5 6 8 10</t>
         </is>
       </c>
       <c r="I34" s="36" t="inlineStr">
         <is>
-          <t>узел 2 листа 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>выше дренажа на 0,235 м (узел 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
           <t>27</t>
@@ -1951,21 +1947,21 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Наружная гидроизоляция колец КЛ-1 битумной мастикой в 2 слоя</t>
+          <t>Подключение выпусков стояков водостоков к кольцам К2 (отводы 45°, косые тройники)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D35" s="32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E35" s="33" t="n"/>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 38</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 32</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -1975,12 +1971,16 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>8 10</t>
-        </is>
-      </c>
-      <c r="I35" s="36" t="n"/>
-    </row>
-    <row r="36" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>5 6 8 10</t>
+        </is>
+      </c>
+      <c r="I35" s="36" t="inlineStr">
+        <is>
+          <t>ориентировочно 8 шт. — по привязке воронок</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A36" s="30" t="inlineStr">
         <is>
           <t>28</t>
@@ -1988,21 +1988,21 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>Устройство вводов и выпуска КЛ-1: манжеты, обратный клапан на дренаже, решётка-корзина</t>
+          <t>Установка футляров Ø160 в край плиты для выпусков водостоков</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E36" s="33" t="n"/>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 39, 40, 41, 42</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 33</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -2012,10 +2012,14 @@
       </c>
       <c r="H36" s="30" t="inlineStr">
         <is>
-          <t>6 8 10</t>
-        </is>
-      </c>
-      <c r="I36" s="36" t="n"/>
+          <t>8 10</t>
+        </is>
+      </c>
+      <c r="I36" s="36" t="inlineStr">
+        <is>
+          <t>при бетонировании (КР)</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A37" s="30" t="inlineStr">
@@ -2025,21 +2029,21 @@
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>Прокладка выпуска ПЭ 100 SDR17 63×3,8 и подключение к выпуску ЛК электросварной муфтой</t>
+          <t>Монтаж колодца КЛ-1 из сборных ж/б элементов (днище, кольца, плита, горловина, люк Т, скобы)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="33" t="n"/>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 25, 26</t>
+          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 34, 35, 36, 37, 38, 39, 40</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -2049,53 +2053,75 @@
       </c>
       <c r="H37" s="30" t="inlineStr">
         <is>
-          <t>3 6 10</t>
+          <t>3 6 8 10</t>
         </is>
       </c>
       <c r="I37" s="36" t="inlineStr">
         <is>
-          <t>с допуском ООО «Лика»</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t>Дренаж Др</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="n"/>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="29" t="n"/>
+          <t>узел 2 листа 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>Наружная гидроизоляция колец КЛ-1 битумной мастикой в 2 слоя</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 41</t>
+        </is>
+      </c>
+      <c r="G38" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H38" s="30" t="inlineStr">
+        <is>
+          <t>8 10</t>
+        </is>
+      </c>
+      <c r="I38" s="36" t="n"/>
     </row>
     <row r="39" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A39" s="30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>Прокладка дренажных труб перфорированных Ø110 в геотекстиле с уклоном 0,005</t>
+          <t>Устройство вводов и выпуска КЛ-1: манжеты, обратный клапан на дренаже, решётка-корзина</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D39" s="32" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 43</t>
+          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 42, 43, 44, 45</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2105,20 +2131,20 @@
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 8 10</t>
+          <t>6 8 10 11</t>
         </is>
       </c>
       <c r="I39" s="36" t="n"/>
     </row>
-    <row r="40" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="40" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A40" s="30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>Прокладка транзитных труб ПП SN8 Ø110 без перфорации</t>
+          <t>Прокладка выпуска ПЭ 100 SDR17 63×3,8 и подключение к выпуску ЛК электросварной муфтой</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -2127,12 +2153,12 @@
         </is>
       </c>
       <c r="D40" s="32" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 44</t>
+          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 28, 29</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2142,86 +2168,90 @@
       </c>
       <c r="H40" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 10</t>
-        </is>
-      </c>
-      <c r="I40" s="36" t="n"/>
-    </row>
-    <row r="41" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="inlineStr">
-        <is>
-          <t>Установка дренажных колодцев Ø315 (шахта, днище, крышка, уплотнители)</t>
-        </is>
-      </c>
-      <c r="C41" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 45, 46, 47</t>
-        </is>
-      </c>
-      <c r="G41" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H41" s="30" t="inlineStr">
+          <t>3 6 10</t>
+        </is>
+      </c>
+      <c r="I40" s="36" t="inlineStr">
+        <is>
+          <t>с допуском ООО «Лика»</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>Дренаж Др</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n"/>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="29" t="n"/>
+    </row>
+    <row r="42" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка дренажных труб перфорированных Ø110 в геотекстиле с уклоном 0,003 (дом) и 0,005 (баня)</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="E42" s="33" t="n"/>
+      <c r="F42" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 46</t>
+        </is>
+      </c>
+      <c r="G42" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H42" s="30" t="inlineStr">
         <is>
           <t>3 5 6 8 11</t>
         </is>
       </c>
-      <c r="I41" s="36" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A42" s="27" t="inlineStr">
-        <is>
-          <t>Утепление</t>
-        </is>
-      </c>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="D42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28" t="n"/>
-      <c r="I42" s="29" t="n"/>
-    </row>
-    <row r="43" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="I42" s="36" t="n"/>
+    </row>
+    <row r="43" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>Утепление трубопроводов плитами ЭППС 50 мм на участках малого заглубления</t>
+          <t>Прокладка транзитных труб ПП SN8 Ø110 без перфорации</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 51</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 47</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2231,152 +2261,118 @@
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
+          <t>3 5 6 11</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="n"/>
+    </row>
+    <row r="44" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>Установка дренажных колодцев Ø315 (шахта, днище, крышка или люк Т на опорном кольце, уплотнители)</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" s="33" t="n"/>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 48, 49, 50, 51</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>3 5 6 8 11</t>
+        </is>
+      </c>
+      <c r="I44" s="36" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>Утепление</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="29" t="n"/>
+    </row>
+    <row r="46" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>Утепление трубопроводов плитами ЭППС 50 мм на участках малого заглубления</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="33" t="n"/>
+      <c r="F46" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 55</t>
+        </is>
+      </c>
+      <c r="G46" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H46" s="30" t="inlineStr">
+        <is>
           <t>4 6 8 11</t>
         </is>
       </c>
-      <c r="I43" s="36" t="inlineStr">
+      <c r="I46" s="36" t="inlineStr">
         <is>
           <t>узел 6 листа 8</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A44" s="27" t="inlineStr">
+    <row r="47" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Испытания и сдача</t>
         </is>
       </c>
-      <c r="B44" s="28" t="n"/>
-      <c r="C44" s="28" t="n"/>
-      <c r="D44" s="28" t="n"/>
-      <c r="E44" s="28" t="n"/>
-      <c r="F44" s="28" t="n"/>
-      <c r="G44" s="28" t="n"/>
-      <c r="H44" s="28" t="n"/>
-      <c r="I44" s="29" t="n"/>
-    </row>
-    <row r="45" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>Гидравлическое испытание трубопроводов В1 давлением 1,0 МПа</t>
-        </is>
-      </c>
-      <c r="C45" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E45" s="33" t="inlineStr">
-        <is>
-          <t>17 + 3 = 20</t>
-        </is>
-      </c>
-      <c r="F45" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 2, 7; И05.09.26-НВК.СО, поз. 1, 2</t>
-        </is>
-      </c>
-      <c r="G45" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H45" s="30" t="inlineStr">
-        <is>
-          <t>2 7 9</t>
-        </is>
-      </c>
-      <c r="I45" s="36" t="n"/>
-    </row>
-    <row r="46" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A46" s="30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>Промывка и дезинфекция трубопроводов В1</t>
-        </is>
-      </c>
-      <c r="C46" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E46" s="33" t="inlineStr">
-        <is>
-          <t>17 + 3 = 20</t>
-        </is>
-      </c>
-      <c r="F46" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 2, 7; И05.09.26-НВК.СО, поз. 1, 2</t>
-        </is>
-      </c>
-      <c r="G46" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H46" s="30" t="inlineStr">
-        <is>
-          <t>2 7 9</t>
-        </is>
-      </c>
-      <c r="I46" s="36" t="n"/>
-    </row>
-    <row r="47" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="inlineStr">
-        <is>
-          <t>Испытание трубопроводов К1 и К2 наполнением водой до засыпки</t>
-        </is>
-      </c>
-      <c r="C47" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D47" s="32" t="n">
-        <v>236</v>
-      </c>
-      <c r="E47" s="33" t="inlineStr">
-        <is>
-          <t>62 + 8 + 164 + 2 = 236</t>
-        </is>
-      </c>
-      <c r="F47" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 15, 16, 24, 25</t>
-        </is>
-      </c>
-      <c r="G47" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H47" s="30" t="inlineStr">
-        <is>
-          <t>2 4 5 6 9 10</t>
-        </is>
-      </c>
-      <c r="I47" s="36" t="n"/>
+      <c r="B47" s="28" t="n"/>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="29" t="n"/>
     </row>
     <row r="48" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A48" s="30" t="inlineStr">
@@ -2386,7 +2382,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>Проверка дренажа проливом водой</t>
+          <t>Гидравлическое испытание трубопроводов В1 давлением 1,0 МПа</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -2395,16 +2391,16 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="E48" s="33" t="inlineStr">
         <is>
-          <t>150 + 10 = 160</t>
+          <t>17 + 48 = 65</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 43, 44</t>
+          <t>И05.09.26-НВК, см. листы 2, 7; И05.09.26-НВК.СО, поз. 1, 2</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2414,7 +2410,7 @@
       </c>
       <c r="H48" s="30" t="inlineStr">
         <is>
-          <t>2 5 6 10</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="I48" s="36" t="n"/>
@@ -2427,38 +2423,158 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
+          <t>Промывка и дезинфекция трубопроводов В1</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>17 + 48 = 65</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 2, 7; И05.09.26-НВК.СО, поз. 1, 2</t>
+        </is>
+      </c>
+      <c r="G49" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H49" s="30" t="inlineStr">
+        <is>
+          <t>2 7 9</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="n"/>
+    </row>
+    <row r="50" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>Испытание трубопроводов К1 и К2 наполнением водой до засыпки</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="n">
+        <v>237</v>
+      </c>
+      <c r="E50" s="33" t="inlineStr">
+        <is>
+          <t>62 + 8 + 165 + 2 = 237</t>
+        </is>
+      </c>
+      <c r="F50" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 18, 19, 27, 28</t>
+        </is>
+      </c>
+      <c r="G50" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H50" s="30" t="inlineStr">
+        <is>
+          <t>2 4 5 6 9 10</t>
+        </is>
+      </c>
+      <c r="I50" s="36" t="n"/>
+    </row>
+    <row r="51" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>Проверка дренажа проливом водой</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>160</v>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>150 + 10 = 160</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 46, 47</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>2 5 6 11</t>
+        </is>
+      </c>
+      <c r="I51" s="36" t="n"/>
+    </row>
+    <row r="52" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
           <t>Исполнительная геодезическая съёмка сетей и колодцев до засыпки</t>
         </is>
       </c>
-      <c r="C49" s="32" t="inlineStr">
+      <c r="C52" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D49" s="32" t="n">
-        <v>224.7</v>
-      </c>
-      <c r="E49" s="33" t="n"/>
-      <c r="F49" s="34" t="inlineStr">
+      <c r="D52" s="32" t="n">
+        <v>268.1</v>
+      </c>
+      <c r="E52" s="33" t="n"/>
+      <c r="F52" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-НВК, см. лист 2</t>
         </is>
       </c>
-      <c r="G49" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H49" s="30" t="inlineStr">
+      <c r="G52" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H52" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I49" s="36" t="n"/>
-    </row>
-    <row r="50" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
-    <row r="51" ht="45.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
-    <row r="52" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
+      <c r="I52" s="36" t="n"/>
+    </row>
     <row r="53" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
     <row r="54" ht="38.25" customFormat="1" customHeight="1" s="4" thickBot="1"/>
     <row r="55" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
@@ -2467,14 +2583,14 @@
     <row r="58" ht="15.75" customHeight="1" thickBot="1"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A45:I45"/>
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A44:I44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="55" fitToHeight="0" fitToWidth="1"/>
@@ -2507,10 +2623,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="38" t="inlineStr">
         <is>
-          <t>2. Земляные работы — по траншеям шириной по дну 0,7 м (одна труба) и 0,9 м (общая траншея дренажа и К2) от проектной поверхности (планировка у зданий −0,300 — допущение, лист 2); стенки вертикальные, глубже 1,5 м — в креплении. При работе с откосами объём разработки и засыпки уточняется.</t>
+          <t>2. Земляные работы — по траншеям шириной по дну 0,7 м (одна труба) и 0,9 м (общая траншея дренажа и К2) от планировки участка 186,65 (Заказчик); стенки вертикальные, глубже 1,5 м — в креплении. При работе с откосами объём разработки и засыпки уточняется. В зоне заезда (полоса 3,2 м вдоль западного и восточного заборов, площадка у гаража) — засыпка песком на всю глубину и люки Т (C250).</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>325.5</v>
+        <v>323.4</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 301,3 + котлованы 24,2 = 325,5</t>
+          <t>траншеи 299,2 + котлованы 24,2 = 323,4</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1132,7 +1132,7 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 52</t>
+          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 53</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1168,12 +1168,12 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>85.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 52</t>
+          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 53</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1214,7 +1214,7 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 53</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 54</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>геотекстиль — поз. 54</t>
+          <t>геотекстиль — поз. 55</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 54</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 55</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>158.6</v>
+        <v>157.3</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>339,4 − 180,8 = 158,6</t>
+          <t>337,3 − 180,1 = 157,3</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>180.8</v>
+        <v>180.1</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       <c r="E20" s="33" t="n"/>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 2, 10, 11</t>
+          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 2, 10, 11, 12</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="I20" s="36" t="inlineStr">
         <is>
-          <t>уклон к КП-1: 0,01 и 0,003; глубина В1-Бс 0,7–0,8 м</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>уклон к КП-1: 0,01 и 0,003; до верха трубы: КХ-8н 0,79–0,81 м, В1-Бс 0,61–0,74 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A21" s="30" t="inlineStr">
         <is>
           <t>15</t>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Протаскивание линии В1-Бс в футляре ПНД Ø63 в зоне заезда</t>
+          <t>Протаскивание линий В1-Бс и КХ-8н в футлярах ПНД Ø63 (зона заезда, пересечения с К1, К2)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -1458,12 +1458,12 @@
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E21" s="33" t="n"/>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 3; И05.09.26-НВК.СО, поз. 15</t>
+          <t>И05.09.26-НВК, см. лист 3; И05.09.26-НВК.СО, поз. 16</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="E22" s="33" t="n"/>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 14</t>
+          <t>И05.09.26-НВК, см. листы 3, 7; И05.09.26-НВК.СО, поз. 15</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="E26" s="33" t="n"/>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 7, 8; И05.09.26-НВК.СО, поз. 12, 13, 16</t>
+          <t>И05.09.26-НВК, см. листы 3, 7, 8; И05.09.26-НВК.СО, поз. 13, 14, 17</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1749,7 +1749,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 18, 20</t>
+          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 19, 21</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
-          <t>3 4 9</t>
+          <t>3 4 10</t>
         </is>
       </c>
       <c r="I29" s="36" t="n"/>
@@ -1786,7 +1786,7 @@
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 19</t>
+          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 20</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H30" s="30" t="inlineStr">
         <is>
-          <t>3 4 9</t>
+          <t>3 4 10</t>
         </is>
       </c>
       <c r="I30" s="36" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 21, 22, 23</t>
+          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 22, 23, 24</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1864,7 +1864,7 @@
       <c r="E32" s="33" t="n"/>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 24, 25</t>
+          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 25, 26</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -1920,7 +1920,7 @@
       <c r="E34" s="33" t="n"/>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 27, 30, 31, 32</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 28, 31, 32, 33</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -1961,7 +1961,7 @@
       <c r="E35" s="33" t="n"/>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 32</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 33</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -2002,7 +2002,7 @@
       <c r="E36" s="33" t="n"/>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 33</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 34</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -2043,7 +2043,7 @@
       <c r="E37" s="33" t="n"/>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 34, 35, 36, 37, 38, 39, 40</t>
+          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 35, 36, 37, 38, 39, 40, 41</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -2084,7 +2084,7 @@
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 41</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 42</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>8 10</t>
+          <t>8 11</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
@@ -2121,7 +2121,7 @@
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 42, 43, 44, 45</t>
+          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 43, 44, 45, 46</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>6 8 10 11</t>
+          <t>6 8 11</t>
         </is>
       </c>
       <c r="I39" s="36" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 28, 29</t>
+          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 29, 30</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2214,7 +2214,7 @@
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 46</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 47</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2251,7 +2251,7 @@
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 47</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 48</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2288,7 +2288,7 @@
       <c r="E44" s="33" t="n"/>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 48, 49, 50, 51</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 49, 50, 51, 52</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -2340,7 +2340,7 @@
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 55</t>
+          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 56</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 18, 19, 27, 28</t>
+          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 19, 20, 28, 29</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>2 4 5 6 9 10</t>
+          <t>2 4 5 6 10</t>
         </is>
       </c>
       <c r="I50" s="36" t="n"/>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 46, 47</t>
+          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 47, 48</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>4,5 + 5,3 + 4,2 = 13,9</t>
+          <t>3,8 + 5,3 + 4,2 = 13,3</t>
         </is>
       </c>
       <c r="F5" s="34" t="inlineStr">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>268.1</v>
+        <v>217.8</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>323.4</v>
+        <v>265.2</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 299,2 + котлованы 24,2 = 323,4</t>
+          <t>траншеи 245,8 + котлованы 19,4 = 265,2</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>21.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>296.9</v>
+        <v>259.6</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" s="36" t="inlineStr">
         <is>
-          <t>К1-б3, К2-ЛК, В1-н, Др-1/2, Др-2/3, Др-4/3, Др-К</t>
+          <t>К2-ЛК, В1-н, Др-1/2, Др-2/3, Др-4/3, Др-К</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>70.2</v>
+        <v>48.9</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 53</t>
+          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 48</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1168,12 +1168,12 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>84.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 53</t>
+          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 48</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1214,7 +1214,7 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 54</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 49</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>геотекстиль — поз. 55</t>
+          <t>геотекстиль — поз. 50</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 55</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 50</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>157.3</v>
+        <v>138.1</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>337,3 − 180,1 = 157,3</t>
+          <t>278,5 − 140,3 = 138,1</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>180.1</v>
+        <v>140.3</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I20" s="36" t="inlineStr">
         <is>
-          <t>уклон к КП-1: 0,01 и 0,003; до верха трубы: КХ-8н 0,79–0,81 м, В1-Бс 0,61–0,74 м</t>
+          <t>уклон к КП-1: 0,01 и 0,003; до верха трубы: КХ-8н 0,79–0,81 м, В1-Бс 0,48–0,60 м</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       <c r="H28" s="28" t="n"/>
       <c r="I28" s="29" t="n"/>
     </row>
-    <row r="29" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="29" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>22</t>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (выпуски) на песчаном основании</t>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (выпуск К1-1, линия бани через КК-1) на песчаном основании</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -1744,12 +1744,12 @@
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 19, 21</t>
+          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 19</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I29" s="36" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1" thickBot="1">
+    <row r="30" ht="45" customHeight="1" thickBot="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
           <t>23</t>
@@ -1772,21 +1772,21 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø160 (сеть бани) на песчаном основании</t>
+          <t>Установка колодца канализационного полимерного Ø630 КК-1 с лотком, шахтой и люком</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D30" s="32" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4; И05.09.26-НВК.СО, поз. 20</t>
+          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 20</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="H30" s="30" t="inlineStr">
         <is>
-          <t>3 4 10</t>
+          <t>3 4 8 10</t>
         </is>
       </c>
       <c r="I30" s="36" t="n"/>
     </row>
-    <row r="31" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="31" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
           <t>24</t>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>Установка колодцев канализационных полимерных Ø630 с лотком, шахтой и люком</t>
+          <t>Врезка в существующий колодец ДК5-018: алмазное бурение отверстия в ж/б стенке, установка манжеты, заделка, устройство лотка-водослива</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -1818,16 +1818,12 @@
         </is>
       </c>
       <c r="D31" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 + 1 = 3</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 22, 23, 24</t>
+          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 21</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1840,87 +1836,91 @@
           <t>3 4 8 10</t>
         </is>
       </c>
-      <c r="I31" s="36" t="n"/>
-    </row>
-    <row r="32" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="I31" s="36" t="inlineStr">
+        <is>
+          <t>узел 3 листа 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>Ливневая канализация К2. Колодец КЛ-1</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="29" t="n"/>
+    </row>
+    <row r="33" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>Врезка в существующий колодец ДК5-018: алмазное бурение отверстий в ж/б стенке, установка манжет, заделка, устройство лотков-водосливов</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит) с фасонными частями в общей траншее с дренажом</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="n">
+        <v>165</v>
+      </c>
+      <c r="E33" s="33" t="n"/>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 23, 26, 27, 28</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H33" s="30" t="inlineStr">
+        <is>
+          <t>3 5 6 8 10</t>
+        </is>
+      </c>
+      <c r="I33" s="36" t="inlineStr">
+        <is>
+          <t>выше дренажа на 0,235 м (узел 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Подключение выпусков стояков водостоков к кольцам К2 (отводы 45°, косые тройники)</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D32" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="33" t="n"/>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 4, 8; И05.09.26-НВК.СО, поз. 25, 26</t>
-        </is>
-      </c>
-      <c r="G32" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H32" s="30" t="inlineStr">
-        <is>
-          <t>3 4 8 10</t>
-        </is>
-      </c>
-      <c r="I32" s="36" t="inlineStr">
-        <is>
-          <t>узел 3 листа 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>Ливневая канализация К2. Колодец КЛ-1</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="n"/>
-      <c r="C33" s="28" t="n"/>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="n"/>
-      <c r="H33" s="28" t="n"/>
-      <c r="I33" s="29" t="n"/>
-    </row>
-    <row r="34" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит) с фасонными частями в общей траншее с дренажом</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
       <c r="D34" s="32" t="n">
-        <v>165</v>
+        <v>8</v>
       </c>
       <c r="E34" s="33" t="n"/>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 28, 31, 32, 33</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 28</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -1930,16 +1930,16 @@
       </c>
       <c r="H34" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 8 10</t>
+          <t>5 6 8 10</t>
         </is>
       </c>
       <c r="I34" s="36" t="inlineStr">
         <is>
-          <t>выше дренажа на 0,235 м (узел 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>ориентировочно 8 шт. — по привязке воронок</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
           <t>27</t>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Подключение выпусков стояков водостоков к кольцам К2 (отводы 45°, косые тройники)</t>
+          <t>Установка футляров Ø160 в край плиты для выпусков водостоков</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -1961,7 +1961,7 @@
       <c r="E35" s="33" t="n"/>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 33</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 29</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -1971,16 +1971,16 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>5 6 8 10</t>
+          <t>8 10</t>
         </is>
       </c>
       <c r="I35" s="36" t="inlineStr">
         <is>
-          <t>ориентировочно 8 шт. — по привязке воронок</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>при бетонировании (КР)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A36" s="30" t="inlineStr">
         <is>
           <t>28</t>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>Установка футляров Ø160 в край плиты для выпусков водостоков</t>
+          <t>Монтаж колодца КЛ-1 из сборных ж/б элементов (днище, кольца, плита, горловина, люк Т, скобы)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -1997,12 +1997,12 @@
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E36" s="33" t="n"/>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 34</t>
+          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 30, 31, 32, 33, 34, 35, 36</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -2012,16 +2012,16 @@
       </c>
       <c r="H36" s="30" t="inlineStr">
         <is>
-          <t>8 10</t>
+          <t>3 6 8 10</t>
         </is>
       </c>
       <c r="I36" s="36" t="inlineStr">
         <is>
-          <t>при бетонировании (КР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>узел 2 листа 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A37" s="30" t="inlineStr">
         <is>
           <t>29</t>
@@ -2029,21 +2029,21 @@
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>Монтаж колодца КЛ-1 из сборных ж/б элементов (днище, кольца, плита, горловина, люк Т, скобы)</t>
+          <t>Наружная гидроизоляция колец КЛ-1 битумной мастикой в 2 слоя</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E37" s="33" t="n"/>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 35, 36, 37, 38, 39, 40, 41</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 37</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -2053,16 +2053,12 @@
       </c>
       <c r="H37" s="30" t="inlineStr">
         <is>
-          <t>3 6 8 10</t>
-        </is>
-      </c>
-      <c r="I37" s="36" t="inlineStr">
-        <is>
-          <t>узел 2 листа 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>8 10</t>
+        </is>
+      </c>
+      <c r="I37" s="36" t="n"/>
+    </row>
+    <row r="38" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A38" s="30" t="inlineStr">
         <is>
           <t>30</t>
@@ -2070,21 +2066,21 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>Наружная гидроизоляция колец КЛ-1 битумной мастикой в 2 слоя</t>
+          <t>Устройство вводов и выпуска КЛ-1: манжеты, обратный клапан на дренаже, решётка-корзина</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D38" s="32" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 42</t>
+          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 38, 39, 40, 41</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2094,7 +2090,7 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>8 11</t>
+          <t>6 8 10</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
@@ -2107,21 +2103,21 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>Устройство вводов и выпуска КЛ-1: манжеты, обратный клапан на дренаже, решётка-корзина</t>
+          <t>Прокладка выпуска ПЭ 100 SDR17 63×3,8 и подключение к выпуску ЛК электросварной муфтой</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D39" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 43, 44, 45, 46</t>
+          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 24, 25</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2131,68 +2127,68 @@
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>6 8 11</t>
-        </is>
-      </c>
-      <c r="I39" s="36" t="n"/>
-    </row>
-    <row r="40" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A40" s="30" t="inlineStr">
+          <t>3 6 10</t>
+        </is>
+      </c>
+      <c r="I39" s="36" t="inlineStr">
+        <is>
+          <t>с допуском ООО «Лика»</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>Дренаж Др</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="29" t="n"/>
+    </row>
+    <row r="41" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B40" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка выпуска ПЭ 100 SDR17 63×3,8 и подключение к выпуску ЛК электросварной муфтой</t>
-        </is>
-      </c>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка дренажных труб перфорированных Ø110 в геотекстиле с уклоном 0,003 (дом) и 0,005 (баня)</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D40" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="33" t="n"/>
-      <c r="F40" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 29, 30</t>
-        </is>
-      </c>
-      <c r="G40" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H40" s="30" t="inlineStr">
-        <is>
-          <t>3 6 10</t>
-        </is>
-      </c>
-      <c r="I40" s="36" t="inlineStr">
-        <is>
-          <t>с допуском ООО «Лика»</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A41" s="27" t="inlineStr">
-        <is>
-          <t>Дренаж Др</t>
-        </is>
-      </c>
-      <c r="B41" s="28" t="n"/>
-      <c r="C41" s="28" t="n"/>
-      <c r="D41" s="28" t="n"/>
-      <c r="E41" s="28" t="n"/>
-      <c r="F41" s="28" t="n"/>
-      <c r="G41" s="28" t="n"/>
-      <c r="H41" s="28" t="n"/>
-      <c r="I41" s="29" t="n"/>
-    </row>
-    <row r="42" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="D41" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="E41" s="33" t="n"/>
+      <c r="F41" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 42</t>
+        </is>
+      </c>
+      <c r="G41" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H41" s="30" t="inlineStr">
+        <is>
+          <t>3 5 6 8 11</t>
+        </is>
+      </c>
+      <c r="I41" s="36" t="n"/>
+    </row>
+    <row r="42" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A42" s="30" t="inlineStr">
         <is>
           <t>33</t>
@@ -2200,7 +2196,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>Прокладка дренажных труб перфорированных Ø110 в геотекстиле с уклоном 0,003 (дом) и 0,005 (баня)</t>
+          <t>Прокладка транзитных труб ПП SN8 Ø110 без перфорации</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -2209,12 +2205,12 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 47</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 43</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2224,12 +2220,12 @@
       </c>
       <c r="H42" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 8 11</t>
+          <t>3 5 6 11</t>
         </is>
       </c>
       <c r="I42" s="36" t="n"/>
     </row>
-    <row r="43" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="43" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
           <t>34</t>
@@ -2237,21 +2233,21 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>Прокладка транзитных труб ПП SN8 Ø110 без перфорации</t>
+          <t>Установка дренажных колодцев Ø315 (шахта, днище, крышка или люк Т на опорном кольце, уплотнители)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 48</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 44, 45, 46, 47</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2261,118 +2257,122 @@
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 11</t>
+          <t>3 5 6 8 11</t>
         </is>
       </c>
       <c r="I43" s="36" t="n"/>
     </row>
-    <row r="44" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A44" s="30" t="inlineStr">
+    <row r="44" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>Утепление</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="n"/>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="29" t="n"/>
+    </row>
+    <row r="45" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B44" s="31" t="inlineStr">
-        <is>
-          <t>Установка дренажных колодцев Ø315 (шахта, днище, крышка или люк Т на опорном кольце, уплотнители)</t>
-        </is>
-      </c>
-      <c r="C44" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E44" s="33" t="n"/>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 49, 50, 51, 52</t>
-        </is>
-      </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H44" s="30" t="inlineStr">
-        <is>
-          <t>3 5 6 8 11</t>
-        </is>
-      </c>
-      <c r="I44" s="36" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Утепление</t>
-        </is>
-      </c>
-      <c r="B45" s="28" t="n"/>
-      <c r="C45" s="28" t="n"/>
-      <c r="D45" s="28" t="n"/>
-      <c r="E45" s="28" t="n"/>
-      <c r="F45" s="28" t="n"/>
-      <c r="G45" s="28" t="n"/>
-      <c r="H45" s="28" t="n"/>
-      <c r="I45" s="29" t="n"/>
-    </row>
-    <row r="46" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Утепление трубопроводов плитами ЭППС 50 мм на участках малого заглубления</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="33" t="n"/>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 51</t>
+        </is>
+      </c>
+      <c r="G45" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H45" s="30" t="inlineStr">
+        <is>
+          <t>4 6 8 11</t>
+        </is>
+      </c>
+      <c r="I45" s="36" t="inlineStr">
+        <is>
+          <t>узел 6 листа 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>Испытания и сдача</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="29" t="n"/>
+    </row>
+    <row r="47" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>Утепление трубопроводов плитами ЭППС 50 мм на участках малого заглубления</t>
-        </is>
-      </c>
-      <c r="C46" s="32" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" s="33" t="n"/>
-      <c r="F46" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 56</t>
-        </is>
-      </c>
-      <c r="G46" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H46" s="30" t="inlineStr">
-        <is>
-          <t>4 6 8 11</t>
-        </is>
-      </c>
-      <c r="I46" s="36" t="inlineStr">
-        <is>
-          <t>узел 6 листа 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Испытания и сдача</t>
-        </is>
-      </c>
-      <c r="B47" s="28" t="n"/>
-      <c r="C47" s="28" t="n"/>
-      <c r="D47" s="28" t="n"/>
-      <c r="E47" s="28" t="n"/>
-      <c r="F47" s="28" t="n"/>
-      <c r="G47" s="28" t="n"/>
-      <c r="H47" s="28" t="n"/>
-      <c r="I47" s="29" t="n"/>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>Гидравлическое испытание трубопроводов В1 давлением 1,0 МПа</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E47" s="33" t="inlineStr">
+        <is>
+          <t>17 + 48 = 65</t>
+        </is>
+      </c>
+      <c r="F47" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК, см. листы 2, 7; И05.09.26-НВК.СО, поз. 1, 2</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
+        </is>
+      </c>
+      <c r="H47" s="30" t="inlineStr">
+        <is>
+          <t>2 7 9</t>
+        </is>
+      </c>
+      <c r="I47" s="36" t="n"/>
     </row>
     <row r="48" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A48" s="30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>Гидравлическое испытание трубопроводов В1 давлением 1,0 МПа</t>
+          <t>Промывка и дезинфекция трубопроводов В1</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I48" s="36" t="n"/>
     </row>
-    <row r="49" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="49" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A49" s="30" t="inlineStr">
         <is>
           <t>38</t>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>Промывка и дезинфекция трубопроводов В1</t>
+          <t>Испытание трубопроводов К1 и К2 наполнением водой до засыпки</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>17 + 48 = 65</t>
+          <t>14 + 165 + 2 = 181</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 7; И05.09.26-НВК.СО, поз. 1, 2</t>
+          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 19, 23, 24</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>2 7 9</t>
+          <t>2 4 5 6 10</t>
         </is>
       </c>
       <c r="I49" s="36" t="n"/>
     </row>
-    <row r="50" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="50" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="30" t="inlineStr">
         <is>
           <t>39</t>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>Испытание трубопроводов К1 и К2 наполнением водой до засыпки</t>
+          <t>Проверка дренажа проливом водой</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -2473,16 +2473,16 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>237</v>
+        <v>160</v>
       </c>
       <c r="E50" s="33" t="inlineStr">
         <is>
-          <t>62 + 8 + 165 + 2 = 237</t>
+          <t>150 + 10 = 160</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 19, 20, 28, 29</t>
+          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 42, 43</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>2 4 5 6 10</t>
+          <t>2 5 6 11</t>
         </is>
       </c>
       <c r="I50" s="36" t="n"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>Проверка дренажа проливом водой</t>
+          <t>Исполнительная геодезическая съёмка сетей и колодцев до засыпки</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -2514,16 +2514,12 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>160</v>
-      </c>
-      <c r="E51" s="33" t="inlineStr">
-        <is>
-          <t>150 + 10 = 160</t>
-        </is>
-      </c>
+        <v>217.8</v>
+      </c>
+      <c r="E51" s="33" t="n"/>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 47, 48</t>
+          <t>И05.09.26-НВК, см. лист 2</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2533,48 +2529,12 @@
       </c>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>2 5 6 11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" s="36" t="n"/>
     </row>
-    <row r="52" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A52" s="30" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>Исполнительная геодезическая съёмка сетей и колодцев до засыпки</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n">
-        <v>268.1</v>
-      </c>
-      <c r="E52" s="33" t="n"/>
-      <c r="F52" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК, см. лист 2</t>
-        </is>
-      </c>
-      <c r="G52" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-НВК Наружные сети водопровода и канализации</t>
-        </is>
-      </c>
-      <c r="H52" s="30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I52" s="36" t="n"/>
-    </row>
+    <row r="52" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
     <row r="53" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
     <row r="54" ht="38.25" customFormat="1" customHeight="1" s="4" thickBot="1"/>
     <row r="55" ht="30.75" customFormat="1" customHeight="1" s="4" thickBot="1"/>
@@ -2583,14 +2543,14 @@
     <row r="58" ht="15.75" customHeight="1" thickBot="1"/>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A45:I45"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A46:I46"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A44:I44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="55" fitToHeight="0" fitToWidth="1"/>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>217.8</v>
+        <v>221.1</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>265.2</v>
+        <v>267</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 245,8 + котлованы 19,4 = 265,2</t>
+          <t>траншеи 247,6 + котлованы 19,4 = 267,0</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>259.6</v>
+        <v>258.6</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34" t="inlineStr">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>138.1</v>
+        <v>138.9</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>278,5 − 140,3 = 138,1</t>
+          <t>280,2 − 141,4 = 138,9</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>140.3</v>
+        <v>141.4</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" s="33" t="n"/>
       <c r="F21" s="34" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (выпуск К1-1, линия бани через КК-1) на песчаном основании</t>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (выпуск К1-1, две линии бани через КК-1) на песчаном основании</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E45" s="33" t="n"/>
       <c r="F45" s="34" t="inlineStr">
@@ -2432,11 +2432,11 @@
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>14 + 165 + 2 = 181</t>
+          <t>18 + 165 + 2 = 185</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>217.8</v>
+        <v>221.1</v>
       </c>
       <c r="E51" s="33" t="n"/>
       <c r="F51" s="34" t="inlineStr">

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>221.1</v>
+        <v>227.8</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>267</v>
+        <v>275.1</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 247,6 + котлованы 19,4 = 267,0</t>
+          <t>траншеи 255,6 + котлованы 19,5 = 275,1</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>258.6</v>
+        <v>277.4</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" s="36" t="inlineStr">
         <is>
-          <t>К2-ЛК, В1-н, Др-1/2, Др-2/3, Др-4/3, Др-К</t>
+          <t>К2-ЛК, К2-Б (к КЛ-1), В1-н, Др-1/2, Др-2/3, Др-4/3, Др-К</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>138.9</v>
+        <v>140.9</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>280,2 − 141,4 = 138,9</t>
+          <t>288,4 − 147,5 = 140,9</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>141.4</v>
+        <v>147.5</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D33" s="32" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="33" t="n"/>
       <c r="F37" s="34" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>6 8 10</t>
+          <t>6 8 10 11</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
     </row>
-    <row r="39" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="39" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A39" s="30" t="inlineStr">
         <is>
           <t>31</t>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>Прокладка выпуска ПЭ 100 SDR17 63×3,8 и подключение к выпуску ЛК электросварной муфтой</t>
+          <t>Демонтаж участка существующего выпуска ЛК Ø63 в котловане КЛ-1, прокладка выпуска ПЭ 100 SDR17 63×3,8 и врезка в существующий выпуск ЛК электросварной муфтой</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
@@ -2432,11 +2432,11 @@
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>18 + 165 + 2 = 185</t>
+          <t>18 + 169 + 2 = 189</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
@@ -2473,11 +2473,11 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E50" s="33" t="inlineStr">
         <is>
-          <t>150 + 10 = 160</t>
+          <t>150 + 12 = 162</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>221.1</v>
+        <v>227.8</v>
       </c>
       <c r="E51" s="33" t="n"/>
       <c r="F51" s="34" t="inlineStr">

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>227.8</v>
+        <v>234.6</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>275.1</v>
+        <v>278.1</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 255,6 + котлованы 19,5 = 275,1</t>
+          <t>траншеи 256,5 + котлованы 21,6 = 278,1</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34" t="inlineStr">
@@ -1127,12 +1127,12 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>50.7</v>
+        <v>53.9</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 48</t>
+          <t>И05.09.26-НВК, см. листы 4, 5, 6, 7, 8; И05.09.26-НВК.СО, поз. 49</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1173,7 +1173,7 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 48</t>
+          <t>И05.09.26-НВК, см. листы 2, 3, 8; И05.09.26-НВК.СО, поз. 49</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1214,7 +1214,7 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 49</t>
+          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 50</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>геотекстиль — поз. 50</t>
+          <t>геотекстиль — поз. 51</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 50</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 51</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>288,4 − 147,5 = 140,9</t>
+          <t>291,4 − 150,5 = 140,9</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>147.5</v>
+        <v>150.5</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
       <c r="H32" s="28" t="n"/>
       <c r="I32" s="29" t="n"/>
     </row>
-    <row r="33" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="33" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
           <t>25</t>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит) с фасонными частями в общей траншее с дренажом</t>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит, подводки от дождеприёмников) с фасонными частями, кольца — в общей траншее с дренажом</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -1874,12 +1874,12 @@
         </is>
       </c>
       <c r="D33" s="32" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 23, 26, 27, 28</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 23, 28, 29, 30</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="34" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
           <t>26</t>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>Подключение выпусков стояков водостоков к кольцам К2 (отводы 45°, косые тройники)</t>
+          <t>Установка дождеприёмников 300×300 с корзиной у наружных граней стен под выпуски водостоков (основание — песок 100 мм, верх в уровне покрытия отмостки −0,020)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -1915,12 +1915,12 @@
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" s="33" t="n"/>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 5, 6, 8; И05.09.26-НВК.СО, поз. 28</t>
+          <t>И05.09.26-НВК, см. листы 3, 5; И05.09.26-НВК.СО, поз. 24, 25</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -1930,16 +1930,16 @@
       </c>
       <c r="H34" s="30" t="inlineStr">
         <is>
-          <t>5 6 8 10</t>
+          <t>3 5 10</t>
         </is>
       </c>
       <c r="I34" s="36" t="inlineStr">
         <is>
-          <t>ориентировочно 8 шт. — по привязке воронок</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>дом — ДК-1…ДК-8 по ведомости (лист 3), баня — 2 ориентировочно; узел 9 листа 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
           <t>27</t>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Установка футляров Ø160 в край плиты для выпусков водостоков</t>
+          <t>Подключение подводок от дождеприёмников к кольцам К2 (ПП SN8 Ø110 под утеплённой отмосткой, отвод 45° вниз, косой тройник 45°)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -1956,12 +1956,12 @@
         </is>
       </c>
       <c r="D35" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E35" s="33" t="n"/>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 29</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 30</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>8 10</t>
+          <t>3 5 6 10</t>
         </is>
       </c>
       <c r="I35" s="36" t="inlineStr">
         <is>
-          <t>при бетонировании (КР)</t>
+          <t>10 шт.: дом 8 — места врезок на профилях листа 5, баня 2 — ориентировочно</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       <c r="E36" s="33" t="n"/>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 30, 31, 32, 33, 34, 35, 36</t>
+          <t>И05.09.26-НВК, см. листы 3, 6, 8; И05.09.26-НВК.СО, поз. 31, 32, 33, 34, 35, 36, 37</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -2043,7 +2043,7 @@
       <c r="E37" s="33" t="n"/>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 37</t>
+          <t>И05.09.26-НВК, см. лист 8; И05.09.26-НВК.СО, поз. 38</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 38, 39, 40, 41</t>
+          <t>И05.09.26-НВК, см. листы 6, 8; И05.09.26-НВК.СО, поз. 39, 40, 41, 42</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>6 8 10 11</t>
+          <t>6 8 11</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
@@ -2117,7 +2117,7 @@
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 24, 25</t>
+          <t>И05.09.26-НВК, см. листы 3, 6; И05.09.26-НВК.СО, поз. 26, 27</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2173,7 +2173,7 @@
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 42</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 43</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 43</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6; И05.09.26-НВК.СО, поз. 44</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2247,7 +2247,7 @@
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 44, 45, 46, 47</t>
+          <t>И05.09.26-НВК, см. листы 3, 5, 6, 8; И05.09.26-НВК.СО, поз. 45, 46, 47, 48</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2299,7 +2299,7 @@
       <c r="E45" s="33" t="n"/>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 51</t>
+          <t>И05.09.26-НВК, см. листы 4, 6, 8; И05.09.26-НВК.СО, поз. 52</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>18 + 169 + 2 = 189</t>
+          <t>18 + 178 + 2 = 198</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 19, 23, 24</t>
+          <t>И05.09.26-НВК, см. листы 2, 4, 5, 6; И05.09.26-НВК.СО, поз. 19, 23, 26</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 42, 43</t>
+          <t>И05.09.26-НВК, см. листы 2, 5, 6; И05.09.26-НВК.СО, поз. 43, 44</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>227.8</v>
+        <v>234.6</v>
       </c>
       <c r="E51" s="33" t="n"/>
       <c r="F51" s="34" t="inlineStr">
@@ -2593,14 +2593,14 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t>3. Количество фасонных частей подсчитано по модели и уточняется по месту в пределах общего объёма работ; выпуски водостоков (8 шт.) — ориентировочно, до привязки воронок Заказчиком.</t>
+          <t>3. Количество фасонных частей подсчитано по модели и уточняется по месту в пределах общего объёма работ; дождеприёмники и подводки бани (2 шт.) — ориентировочно, до привязки водостоков бани.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>4. Ввод В1, выпуски К1, подводка КХ-8 и выпуск лотка гаража до наружной грани фундамента, стояки водостоков — раздел ВК; утеплённая отмостка — КР/АР; питание греющего кабеля — ЭОМ.</t>
+          <t>4. Ввод В1, выпуски К1, подводка КХ-8 и выпуск лотка гаража до наружной грани фундамента, стояки водостоков с выпусками сквозь стену в ДК (чугун SML) — раздел ВК; утеплённая отмостка — КР/АР; питание греющего кабеля — ЭОМ.</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>234.6</v>
+        <v>235.7</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>278.1</v>
+        <v>278.8</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>траншеи 256,5 + котлованы 21,6 = 278,1</t>
+          <t>траншеи 256,7 + котлованы 22,1 = 278,8</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34" t="inlineStr">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>53.9</v>
+        <v>49.2</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>140.9</v>
+        <v>146.2</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>291,4 − 150,5 = 140,9</t>
+          <t>292,1 − 145,9 = 146,2</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>150.5</v>
+        <v>145.9</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr"/>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольца К2 дома и бани, транзит, подводки от дождеприёмников) с фасонными частями, кольца — в общей траншее с дренажом</t>
+          <t>Прокладка трубопроводов ПП SN8 Ø110 (кольцо К2 дома, ветка К2 бани, транзит, подводки от дождеприёмников) с фасонными частями, кольцо и ветка — в общей траншее с дренажом</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D33" s="32" t="n">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
@@ -1935,11 +1935,11 @@
       </c>
       <c r="I34" s="36" t="inlineStr">
         <is>
-          <t>дом — ДК-1…ДК-8 по ведомости (лист 3), баня — 2 ориентировочно; узел 9 листа 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>дом — ДК-1…ДК-8, баня — ДК-б1, ДК-б2 (наружные водостоки) по ведомости (лист 3); узел 9 листа 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
           <t>27</t>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Подключение подводок от дождеприёмников к кольцам К2 (ПП SN8 Ø110 под утеплённой отмосткой, отвод 45° вниз, косой тройник 45°)</t>
+          <t>Подключение подводок от дождеприёмников к К2 (ПП SN8 Ø110 под утеплённой отмосткой, отвод 45° вниз, косой тройник 45°; ДК-б1 — отводом в начало ветки К2 бани)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I35" s="36" t="inlineStr">
         <is>
-          <t>10 шт.: дом 8 — места врезок на профилях листа 5, баня 2 — ориентировочно</t>
+          <t>10 шт.: дом 8, баня 2 — места врезок на профилях листов 5 и 6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="H37" s="30" t="inlineStr">
         <is>
-          <t>8 10</t>
+          <t>8 11</t>
         </is>
       </c>
       <c r="I37" s="36" t="n"/>
@@ -2432,11 +2432,11 @@
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>18 + 178 + 2 = 198</t>
+          <t>18 + 141 + 2 = 161</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>234.6</v>
+        <v>235.7</v>
       </c>
       <c r="E51" s="33" t="n"/>
       <c r="F51" s="34" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t>3. Количество фасонных частей подсчитано по модели и уточняется по месту в пределах общего объёма работ; дождеприёмники и подводки бани (2 шт.) — ориентировочно, до привязки водостоков бани.</t>
+          <t>3. Количество фасонных частей подсчитано по модели и уточняется по месту в пределах общего объёма работ.</t>
         </is>
       </c>
     </row>
